--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-06.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-06.xlsx
@@ -1765,7 +1765,7 @@
     <t>Metropolitanos</t>
   </si>
   <si>
-    <t>2026-09-04 19:39:03</t>
+    <t>2026-09-04 22:10:41</t>
   </si>
 </sst>
 </file>
@@ -2359,22 +2359,22 @@
         <v>390</v>
       </c>
       <c r="F2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -2386,22 +2386,22 @@
         <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
         <v>2.04</v>
@@ -2413,16 +2413,16 @@
         <v>1.81</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>8.6</v>
@@ -2431,61 +2431,61 @@
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK2">
         <v>26</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>810</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
         <v>38</v>
@@ -2494,31 +2494,31 @@
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BF2">
         <v>18</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2616,13 +2616,13 @@
         <v>3.75</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.32</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
         <v>3.55</v>
@@ -2637,16 +2637,16 @@
         <v>1.88</v>
       </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S3">
         <v>2.96</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
         <v>1.28</v>
@@ -2667,10 +2667,10 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD3">
         <v>1000</v>
@@ -2679,10 +2679,10 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -2694,7 +2694,7 @@
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -2715,46 +2715,46 @@
         <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -2843,7 +2843,7 @@
         <v>392</v>
       </c>
       <c r="F4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
         <v>2.54</v>
@@ -2852,13 +2852,13 @@
         <v>3.55</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
         <v>2.82</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -2867,7 +2867,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
         <v>1.1</v>
@@ -2903,7 +2903,7 @@
         <v>1000</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -2951,58 +2951,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AR4">
         <v>1.11</v>
       </c>
       <c r="AS4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AU4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AV4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AW4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AX4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AY4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BA4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BB4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BD4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BE4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG4">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -3100,7 +3100,7 @@
         <v>5.3</v>
       </c>
       <c r="K5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L5">
         <v>1.25</v>
@@ -3115,7 +3115,7 @@
         <v>1.16</v>
       </c>
       <c r="P5">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q5">
         <v>1.49</v>
@@ -3136,7 +3136,7 @@
         <v>1.15</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X5">
         <v>75</v>
@@ -3178,7 +3178,7 @@
         <v>14</v>
       </c>
       <c r="AK5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
         <v>28</v>
@@ -3214,7 +3214,7 @@
         <v>17.5</v>
       </c>
       <c r="AW5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX5">
         <v>10</v>
@@ -3238,10 +3238,10 @@
         <v>18</v>
       </c>
       <c r="BE5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG5">
         <v>32</v>
@@ -3327,16 +3327,16 @@
         <v>394</v>
       </c>
       <c r="F6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G6">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H6">
         <v>3.8</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J6">
         <v>4.3</v>
@@ -3351,22 +3351,22 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O6">
         <v>1.14</v>
       </c>
       <c r="P6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
         <v>1.45</v>
       </c>
       <c r="R6">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T6">
         <v>1.47</v>
@@ -3378,7 +3378,7 @@
         <v>1.33</v>
       </c>
       <c r="W6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X6">
         <v>36</v>
@@ -3393,16 +3393,16 @@
         <v>80</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC6">
         <v>11.5</v>
       </c>
       <c r="AD6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF6">
         <v>18</v>
@@ -3414,7 +3414,7 @@
         <v>15</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
         <v>25</v>
@@ -3468,7 +3468,7 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB6">
         <v>20</v>
@@ -3486,7 +3486,7 @@
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3569,25 +3569,25 @@
         <v>395</v>
       </c>
       <c r="F7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7">
         <v>2.36</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -3599,7 +3599,7 @@
         <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>1.59</v>
@@ -3611,10 +3611,10 @@
         <v>2.46</v>
       </c>
       <c r="T7">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U7">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
         <v>1.45</v>
@@ -3623,28 +3623,28 @@
         <v>1.73</v>
       </c>
       <c r="X7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AB7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF7">
         <v>19.5</v>
@@ -3653,13 +3653,13 @@
         <v>13</v>
       </c>
       <c r="AH7">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK7">
         <v>28</v>
@@ -3668,31 +3668,31 @@
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO7">
         <v>21</v>
       </c>
       <c r="AP7">
+        <v>17.5</v>
+      </c>
+      <c r="AQ7">
+        <v>16</v>
+      </c>
+      <c r="AR7">
         <v>18</v>
       </c>
-      <c r="AQ7">
-        <v>15</v>
-      </c>
-      <c r="AR7">
-        <v>17</v>
-      </c>
       <c r="AS7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT7">
         <v>12</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV7">
         <v>12.5</v>
@@ -3701,34 +3701,34 @@
         <v>20</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD7">
         <v>18</v>
       </c>
       <c r="BE7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF7">
         <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3850,10 +3850,10 @@
         <v>1.55</v>
       </c>
       <c r="S8">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
         <v>2.24</v>
@@ -3970,7 +3970,7 @@
         <v>1.68</v>
       </c>
       <c r="BG8">
-        <v>18</v>
+        <v>2.08</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -4053,7 +4053,7 @@
         <v>397</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
         <v>1.66</v>
@@ -4062,10 +4062,10 @@
         <v>5.5</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="K9">
         <v>4.6</v>
@@ -4092,7 +4092,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -4301,7 +4301,7 @@
         <v>2.6</v>
       </c>
       <c r="H10">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I10">
         <v>2.78</v>
@@ -4328,7 +4328,7 @@
         <v>2.64</v>
       </c>
       <c r="Q10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R10">
         <v>1.66</v>
@@ -4340,7 +4340,7 @@
         <v>1.53</v>
       </c>
       <c r="U10">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V10">
         <v>1.56</v>
@@ -4352,7 +4352,7 @@
         <v>25</v>
       </c>
       <c r="Y10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z10">
         <v>22</v>
@@ -4376,7 +4376,7 @@
         <v>22</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>14.5</v>
@@ -4397,7 +4397,7 @@
         <v>55</v>
       </c>
       <c r="AN10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO10">
         <v>15.5</v>
@@ -4537,16 +4537,16 @@
         <v>399</v>
       </c>
       <c r="F11">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G11">
         <v>3.05</v>
       </c>
       <c r="H11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I11">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J11">
         <v>3.7</v>
@@ -4585,7 +4585,7 @@
         <v>2.48</v>
       </c>
       <c r="V11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
         <v>1.49</v>
@@ -4657,7 +4657,7 @@
         <v>21</v>
       </c>
       <c r="AT11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU11">
         <v>8</v>
@@ -4803,7 +4803,7 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="O12">
         <v>1.29</v>
@@ -4812,7 +4812,7 @@
         <v>2.02</v>
       </c>
       <c r="Q12">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
         <v>1.33</v>
@@ -5278,7 +5278,7 @@
         <v>3.1</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L14">
         <v>1.31</v>
@@ -5305,7 +5305,7 @@
         <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U14">
         <v>1.01</v>
@@ -5517,7 +5517,7 @@
         <v>6.6</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K15">
         <v>5.3</v>
@@ -5559,31 +5559,31 @@
         <v>2.84</v>
       </c>
       <c r="X15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Y15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z15">
+        <v>65</v>
+      </c>
+      <c r="AA15">
+        <v>180</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <v>28</v>
+      </c>
+      <c r="AE15">
         <v>70</v>
       </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>15.5</v>
-      </c>
-      <c r="AC15">
-        <v>14.5</v>
-      </c>
-      <c r="AD15">
-        <v>25</v>
-      </c>
-      <c r="AE15">
-        <v>80</v>
-      </c>
       <c r="AF15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG15">
         <v>11</v>
@@ -5595,46 +5595,46 @@
         <v>65</v>
       </c>
       <c r="AJ15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL15">
         <v>25</v>
       </c>
       <c r="AM15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15">
         <v>5.2</v>
       </c>
       <c r="AO15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP15">
         <v>19.5</v>
       </c>
       <c r="AQ15">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AR15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AS15">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AT15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU15">
         <v>11</v>
       </c>
       <c r="AV15">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AW15">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AX15">
         <v>11</v>
@@ -5646,22 +5646,22 @@
         <v>16.5</v>
       </c>
       <c r="BA15">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BB15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC15">
         <v>13</v>
       </c>
       <c r="BD15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BE15">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG15">
         <v>32</v>
@@ -5777,22 +5777,22 @@
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q16">
         <v>1.59</v>
       </c>
       <c r="R16">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S16">
         <v>2.46</v>
       </c>
       <c r="T16">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U16">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V16">
         <v>1.43</v>
@@ -5816,13 +5816,13 @@
         <v>18.5</v>
       </c>
       <c r="AC16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD16">
         <v>17</v>
       </c>
       <c r="AE16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF16">
         <v>22</v>
@@ -5831,7 +5831,7 @@
         <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
         <v>40</v>
@@ -5870,13 +5870,13 @@
         <v>14</v>
       </c>
       <c r="AU16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16">
         <v>12.5</v>
       </c>
       <c r="AW16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX16">
         <v>16</v>
@@ -5998,7 +5998,7 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
         <v>3.45</v>
@@ -6013,7 +6013,7 @@
         <v>1.07</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O17">
         <v>1.31</v>
@@ -6028,7 +6028,7 @@
         <v>1.39</v>
       </c>
       <c r="S17">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T17">
         <v>1.77</v>
@@ -6040,7 +6040,7 @@
         <v>1.3</v>
       </c>
       <c r="W17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -6067,7 +6067,7 @@
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG17">
         <v>12.5</v>
@@ -6097,16 +6097,16 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AR17">
         <v>18.5</v>
       </c>
       <c r="AS17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AT17">
         <v>8</v>
@@ -6115,10 +6115,10 @@
         <v>5.9</v>
       </c>
       <c r="AV17">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AW17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AX17">
         <v>1.38</v>
@@ -6127,28 +6127,28 @@
         <v>8.4</v>
       </c>
       <c r="AZ17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BA17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BB17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BC17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BD17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BE17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BF17">
         <v>10.5</v>
       </c>
       <c r="BG17">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -6715,13 +6715,13 @@
         <v>408</v>
       </c>
       <c r="F20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G20">
         <v>110</v>
       </c>
       <c r="H20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I20">
         <v>110</v>
@@ -6763,10 +6763,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -7199,22 +7199,22 @@
         <v>410</v>
       </c>
       <c r="F22">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="H22">
         <v>2.18</v>
       </c>
       <c r="I22">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="J22">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.31</v>
@@ -7238,7 +7238,7 @@
         <v>1.38</v>
       </c>
       <c r="S22">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T22">
         <v>1.6</v>
@@ -7247,10 +7247,10 @@
         <v>2.22</v>
       </c>
       <c r="V22">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -7474,7 +7474,7 @@
         <v>2</v>
       </c>
       <c r="Q23">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="R23">
         <v>1.32</v>
@@ -7695,7 +7695,7 @@
         <v>2.38</v>
       </c>
       <c r="J24">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K24">
         <v>3.85</v>
@@ -7728,7 +7728,7 @@
         <v>1.01</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V24">
         <v>1.72</v>
@@ -7925,22 +7925,22 @@
         <v>413</v>
       </c>
       <c r="F25">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H25">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I25">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7949,19 +7949,19 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O25">
         <v>1.26</v>
       </c>
       <c r="P25">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="R25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S25">
         <v>2.84</v>
@@ -7973,10 +7973,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -8081,7 +8081,7 @@
         <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG25">
         <v>1.01</v>
@@ -8167,22 +8167,22 @@
         <v>414</v>
       </c>
       <c r="F26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G26">
         <v>4.9</v>
       </c>
       <c r="H26">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I26">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J26">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
         <v>1.33</v>
@@ -8197,7 +8197,7 @@
         <v>1.25</v>
       </c>
       <c r="P26">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q26">
         <v>1.67</v>
@@ -8209,7 +8209,7 @@
         <v>2.62</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U26">
         <v>1.01</v>
@@ -8218,7 +8218,7 @@
         <v>1.92</v>
       </c>
       <c r="W26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -8326,7 +8326,7 @@
         <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -8409,7 +8409,7 @@
         <v>415</v>
       </c>
       <c r="F27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G27">
         <v>110</v>
@@ -8421,7 +8421,7 @@
         <v>110</v>
       </c>
       <c r="J27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K27">
         <v>410</v>
@@ -8457,7 +8457,7 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W27">
         <v>1.06</v>
@@ -8651,22 +8651,22 @@
         <v>416</v>
       </c>
       <c r="F28">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G28">
-        <v>2.46</v>
+        <v>530</v>
       </c>
       <c r="H28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J28">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K28">
-        <v>3.7</v>
+        <v>230</v>
       </c>
       <c r="L28">
         <v>1.35</v>
@@ -8699,10 +8699,10 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W28">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -9159,7 +9159,7 @@
         <v>1.03</v>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
         <v>1.33</v>
@@ -9177,10 +9177,10 @@
         <v>3.5</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
         <v>1.74</v>
@@ -9377,16 +9377,16 @@
         <v>419</v>
       </c>
       <c r="F31">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G31">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H31">
         <v>6.2</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J31">
         <v>4.1</v>
@@ -9401,43 +9401,43 @@
         <v>1.06</v>
       </c>
       <c r="N31">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P31">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q31">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
         <v>3.2</v>
       </c>
       <c r="T31">
+        <v>1.96</v>
+      </c>
+      <c r="U31">
         <v>1.9</v>
       </c>
-      <c r="U31">
-        <v>1.8</v>
-      </c>
       <c r="V31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W31">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA31">
         <v>1000</v>
@@ -9449,7 +9449,7 @@
         <v>970</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE31">
         <v>1000</v>
@@ -9458,22 +9458,22 @@
         <v>970</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI31">
         <v>1000</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM31">
         <v>1000</v>
@@ -9485,58 +9485,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31">
-        <v>1.3</v>
+        <v>14.5</v>
       </c>
       <c r="AR31">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="AS31">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="AT31">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU31">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AV31">
-        <v>1.3</v>
+        <v>16.5</v>
       </c>
       <c r="AW31">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX31">
-        <v>1.21</v>
+        <v>7.6</v>
       </c>
       <c r="AY31">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AZ31">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="BA31">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB31">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="BC31">
-        <v>1.3</v>
+        <v>13</v>
       </c>
       <c r="BD31">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="BE31">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="BF31">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="BG31">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -9640,13 +9640,13 @@
         <v>1.43</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N32">
         <v>1.48</v>
       </c>
       <c r="O32">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P32">
         <v>1.48</v>
@@ -10393,7 +10393,7 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W35">
         <v>2</v>
@@ -10829,7 +10829,7 @@
         <v>425</v>
       </c>
       <c r="F37">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="G37">
         <v>1.83</v>
@@ -10838,7 +10838,7 @@
         <v>1.1</v>
       </c>
       <c r="I37">
-        <v>110</v>
+        <v>6.8</v>
       </c>
       <c r="J37">
         <v>3.7</v>
@@ -10853,7 +10853,7 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
         <v>1.35</v>
@@ -10862,10 +10862,10 @@
         <v>1.76</v>
       </c>
       <c r="Q37">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="R37">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S37">
         <v>3.55</v>
@@ -10877,7 +10877,7 @@
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W37">
         <v>2.12</v>
@@ -11071,22 +11071,22 @@
         <v>426</v>
       </c>
       <c r="F38">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G38">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H38">
         <v>4</v>
       </c>
       <c r="I38">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="J38">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="K38">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -11119,10 +11119,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W38">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -11343,7 +11343,7 @@
         <v>1.27</v>
       </c>
       <c r="P39">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q39">
         <v>1.74</v>
@@ -11558,7 +11558,7 @@
         <v>3.25</v>
       </c>
       <c r="G40">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H40">
         <v>2.12</v>
@@ -11579,22 +11579,22 @@
         <v>1.03</v>
       </c>
       <c r="N40">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P40">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="R40">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S40">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T40">
         <v>1.5</v>
@@ -11603,10 +11603,10 @@
         <v>2.44</v>
       </c>
       <c r="V40">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X40">
         <v>29</v>
@@ -11833,7 +11833,7 @@
         <v>1.66</v>
       </c>
       <c r="R41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S41">
         <v>2.6</v>
@@ -12039,7 +12039,7 @@
         <v>430</v>
       </c>
       <c r="F42">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G42">
         <v>3.1</v>
@@ -12060,16 +12060,16 @@
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N42">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O42">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P42">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q42">
         <v>2.14</v>
@@ -12078,13 +12078,13 @@
         <v>1.31</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T42">
         <v>1.86</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V42">
         <v>1.6</v>
@@ -12114,10 +12114,10 @@
         <v>12.5</v>
       </c>
       <c r="AE42">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG42">
         <v>14</v>
@@ -12126,7 +12126,7 @@
         <v>19.5</v>
       </c>
       <c r="AI42">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ42">
         <v>180</v>
@@ -12135,22 +12135,22 @@
         <v>38</v>
       </c>
       <c r="AL42">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AM42">
         <v>1000</v>
       </c>
       <c r="AN42">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP42">
         <v>11</v>
       </c>
       <c r="AQ42">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR42">
         <v>14</v>
@@ -12168,7 +12168,7 @@
         <v>11</v>
       </c>
       <c r="AW42">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX42">
         <v>16.5</v>
@@ -12192,7 +12192,7 @@
         <v>28</v>
       </c>
       <c r="BE42">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF42">
         <v>22</v>
@@ -12320,7 +12320,7 @@
         <v>1.4</v>
       </c>
       <c r="S43">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T43">
         <v>1.01</v>
@@ -12529,16 +12529,16 @@
         <v>2.5</v>
       </c>
       <c r="H44">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I44">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J44">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K44">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -12547,7 +12547,7 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="O44">
         <v>1.22</v>
@@ -12556,7 +12556,7 @@
         <v>2.08</v>
       </c>
       <c r="Q44">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="R44">
         <v>1.44</v>
@@ -12571,7 +12571,7 @@
         <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
         <v>1.66</v>
@@ -12795,7 +12795,7 @@
         <v>1.16</v>
       </c>
       <c r="P45">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q45">
         <v>1.53</v>
@@ -13249,16 +13249,16 @@
         <v>435</v>
       </c>
       <c r="F47">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G47">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H47">
         <v>2.1</v>
       </c>
       <c r="I47">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J47">
         <v>1.1</v>
@@ -13285,19 +13285,19 @@
         <v>1.68</v>
       </c>
       <c r="R47">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S47">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="T47">
         <v>1.01</v>
       </c>
       <c r="U47">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V47">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W47">
         <v>1.35</v>
@@ -13494,7 +13494,7 @@
         <v>1.95</v>
       </c>
       <c r="G48">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H48">
         <v>3.65</v>
@@ -13524,13 +13524,13 @@
         <v>2.78</v>
       </c>
       <c r="Q48">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R48">
         <v>1.72</v>
       </c>
       <c r="S48">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T48">
         <v>1.48</v>
@@ -13736,19 +13736,19 @@
         <v>2.98</v>
       </c>
       <c r="G49">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H49">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I49">
         <v>2.4</v>
       </c>
       <c r="J49">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13757,7 +13757,7 @@
         <v>1.03</v>
       </c>
       <c r="N49">
-        <v>2.34</v>
+        <v>5.9</v>
       </c>
       <c r="O49">
         <v>1.17</v>
@@ -13772,7 +13772,7 @@
         <v>1.62</v>
       </c>
       <c r="S49">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T49">
         <v>1.01</v>
@@ -13784,7 +13784,7 @@
         <v>1.71</v>
       </c>
       <c r="W49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X49">
         <v>1000</v>
@@ -13975,22 +13975,22 @@
         <v>438</v>
       </c>
       <c r="F50">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="G50">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H50">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I50">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="J50">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13999,34 +13999,34 @@
         <v>1.04</v>
       </c>
       <c r="N50">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O50">
         <v>1.25</v>
       </c>
       <c r="P50">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q50">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="R50">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S50">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="T50">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="U50">
-        <v>1.08</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W50">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -14047,7 +14047,7 @@
         <v>1000</v>
       </c>
       <c r="AD50">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE50">
         <v>1000</v>
@@ -14077,64 +14077,64 @@
         <v>1000</v>
       </c>
       <c r="AN50">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO50">
         <v>1000</v>
       </c>
       <c r="AP50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV50">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF50">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -14217,19 +14217,19 @@
         <v>439</v>
       </c>
       <c r="F51">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G51">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H51">
         <v>2.42</v>
       </c>
       <c r="I51">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="J51">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K51">
         <v>3.95</v>
@@ -14238,37 +14238,37 @@
         <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N51">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O51">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P51">
         <v>2.16</v>
       </c>
       <c r="Q51">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R51">
         <v>1.46</v>
       </c>
       <c r="S51">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T51">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W51">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X51">
         <v>22</v>
@@ -14361,7 +14361,7 @@
         <v>7.2</v>
       </c>
       <c r="BB51">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC51">
         <v>7</v>
@@ -14462,7 +14462,7 @@
         <v>4.7</v>
       </c>
       <c r="G52">
-        <v>7.8</v>
+        <v>110</v>
       </c>
       <c r="H52">
         <v>1.58</v>
@@ -14471,7 +14471,7 @@
         <v>1.77</v>
       </c>
       <c r="J52">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="K52">
         <v>6.6</v>
@@ -14483,19 +14483,19 @@
         <v>1.01</v>
       </c>
       <c r="N52">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="O52">
         <v>1.16</v>
       </c>
       <c r="P52">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q52">
         <v>1.48</v>
       </c>
       <c r="R52">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="S52">
         <v>2.22</v>
@@ -14510,7 +14510,7 @@
         <v>2.28</v>
       </c>
       <c r="W52">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -14946,7 +14946,7 @@
         <v>2.26</v>
       </c>
       <c r="G54">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H54">
         <v>2.78</v>
@@ -14994,7 +14994,7 @@
         <v>1.43</v>
       </c>
       <c r="W54">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -15191,7 +15191,7 @@
         <v>1.86</v>
       </c>
       <c r="H55">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I55">
         <v>4.8</v>
@@ -15200,7 +15200,7 @@
         <v>4.6</v>
       </c>
       <c r="K55">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -15218,16 +15218,16 @@
         <v>2.44</v>
       </c>
       <c r="Q55">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R55">
         <v>1.76</v>
       </c>
       <c r="S55">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T55">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="U55">
         <v>1.01</v>
@@ -15672,7 +15672,7 @@
         <v>2.12</v>
       </c>
       <c r="G57">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H57">
         <v>2.98</v>
@@ -15693,13 +15693,13 @@
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="O57">
         <v>1.13</v>
       </c>
       <c r="P57">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q57">
         <v>1.4</v>
@@ -15720,7 +15720,7 @@
         <v>1.39</v>
       </c>
       <c r="W57">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -15920,7 +15920,7 @@
         <v>3.75</v>
       </c>
       <c r="I58">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J58">
         <v>3.35</v>
@@ -15935,7 +15935,7 @@
         <v>1.1</v>
       </c>
       <c r="N58">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O58">
         <v>1.45</v>
@@ -15950,7 +15950,7 @@
         <v>1.24</v>
       </c>
       <c r="S58">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T58">
         <v>2.02</v>
@@ -15959,10 +15959,10 @@
         <v>1.71</v>
       </c>
       <c r="V58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W58">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X58">
         <v>10.5</v>
@@ -16013,7 +16013,7 @@
         <v>160</v>
       </c>
       <c r="AN58">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO58">
         <v>85</v>
@@ -16028,7 +16028,7 @@
         <v>22</v>
       </c>
       <c r="AS58">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="AT58">
         <v>7.4</v>
@@ -16040,7 +16040,7 @@
         <v>14</v>
       </c>
       <c r="AW58">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="AX58">
         <v>11.5</v>
@@ -16064,13 +16064,13 @@
         <v>38</v>
       </c>
       <c r="BE58">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF58">
         <v>21</v>
       </c>
       <c r="BG58">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH58">
         <v>1000</v>
@@ -16153,16 +16153,16 @@
         <v>447</v>
       </c>
       <c r="F59">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G59">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J59">
         <v>3.25</v>
@@ -16171,7 +16171,7 @@
         <v>840</v>
       </c>
       <c r="L59">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M59">
         <v>1.01</v>
@@ -16183,10 +16183,10 @@
         <v>1.37</v>
       </c>
       <c r="P59">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Q59">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R59">
         <v>1.2</v>
@@ -16201,7 +16201,7 @@
         <v>1.01</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W59">
         <v>1.41</v>
@@ -16395,13 +16395,13 @@
         <v>448</v>
       </c>
       <c r="F60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G60">
         <v>110</v>
       </c>
       <c r="H60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I60">
         <v>110</v>
@@ -16443,10 +16443,10 @@
         <v>1.01</v>
       </c>
       <c r="V60">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -16640,13 +16640,13 @@
         <v>11.5</v>
       </c>
       <c r="G61">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="H61">
         <v>1.27</v>
       </c>
       <c r="I61">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="J61">
         <v>7</v>
@@ -16667,22 +16667,22 @@
         <v>1.08</v>
       </c>
       <c r="P61">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q61">
         <v>1.08</v>
       </c>
       <c r="R61">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S61">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="T61">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U61">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V61">
         <v>4.4</v>
@@ -16742,58 +16742,58 @@
         <v>1000</v>
       </c>
       <c r="AO61">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AP61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AR61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AU61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AV61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AW61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AX61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AY61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AZ61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BA61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BB61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BC61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BD61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BE61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BF61">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BG61">
         <v>2.84</v>
@@ -16882,7 +16882,7 @@
         <v>1.9</v>
       </c>
       <c r="G62">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H62">
         <v>3.9</v>
@@ -16930,7 +16930,7 @@
         <v>1.23</v>
       </c>
       <c r="W62">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -17127,10 +17127,10 @@
         <v>2.42</v>
       </c>
       <c r="H63">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I63">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J63">
         <v>3.55</v>
@@ -17142,10 +17142,10 @@
         <v>1.01</v>
       </c>
       <c r="M63">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N63">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O63">
         <v>1.28</v>
@@ -17154,7 +17154,7 @@
         <v>1.83</v>
       </c>
       <c r="Q63">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R63">
         <v>1.31</v>
@@ -17390,7 +17390,7 @@
         <v>4.9</v>
       </c>
       <c r="O64">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P64">
         <v>2.44</v>
@@ -17402,16 +17402,16 @@
         <v>1.56</v>
       </c>
       <c r="S64">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="T64">
         <v>1.01</v>
       </c>
       <c r="U64">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V64">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="W64">
         <v>1.53</v>
@@ -17608,7 +17608,7 @@
         <v>1.4</v>
       </c>
       <c r="G65">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H65">
         <v>2.9</v>
@@ -17632,19 +17632,19 @@
         <v>1.96</v>
       </c>
       <c r="O65">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P65">
         <v>1.96</v>
       </c>
       <c r="Q65">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R65">
         <v>1.35</v>
       </c>
       <c r="S65">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T65">
         <v>1.01</v>
@@ -17653,7 +17653,7 @@
         <v>1.01</v>
       </c>
       <c r="V65">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W65">
         <v>2.82</v>
@@ -17847,22 +17847,22 @@
         <v>454</v>
       </c>
       <c r="F66">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="G66">
-        <v>2.78</v>
+        <v>1.87</v>
       </c>
       <c r="H66">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="I66">
-        <v>110</v>
+        <v>7.4</v>
       </c>
       <c r="J66">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K66">
-        <v>600</v>
+        <v>6.2</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -17871,7 +17871,7 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="O66">
         <v>1.22</v>
@@ -17880,13 +17880,13 @@
         <v>2.18</v>
       </c>
       <c r="Q66">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="R66">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="T66">
         <v>1.01</v>
@@ -17895,10 +17895,10 @@
         <v>1.01</v>
       </c>
       <c r="V66">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W66">
-        <v>1.56</v>
+        <v>2.14</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -18095,7 +18095,7 @@
         <v>4.5</v>
       </c>
       <c r="H67">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I67">
         <v>1.84</v>
@@ -18110,7 +18110,7 @@
         <v>1.01</v>
       </c>
       <c r="M67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N67">
         <v>1.01</v>
@@ -18119,16 +18119,16 @@
         <v>1.13</v>
       </c>
       <c r="P67">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q67">
         <v>1.45</v>
       </c>
       <c r="R67">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S67">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="T67">
         <v>1.47</v>
@@ -18334,10 +18334,10 @@
         <v>1.71</v>
       </c>
       <c r="G68">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H68">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I68">
         <v>5.2</v>
@@ -18367,22 +18367,22 @@
         <v>1.14</v>
       </c>
       <c r="R68">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="S68">
         <v>2</v>
       </c>
       <c r="T68">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U68">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V68">
         <v>1.25</v>
       </c>
       <c r="W68">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -18582,10 +18582,10 @@
         <v>2.82</v>
       </c>
       <c r="I69">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J69">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K69">
         <v>3.8</v>
@@ -18621,7 +18621,7 @@
         <v>1.01</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W69">
         <v>1.56</v>
@@ -18818,19 +18818,19 @@
         <v>3.5</v>
       </c>
       <c r="G70">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H70">
         <v>2.04</v>
       </c>
       <c r="I70">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J70">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K70">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18839,7 +18839,7 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="O70">
         <v>1.01</v>
@@ -18851,7 +18851,7 @@
         <v>1.78</v>
       </c>
       <c r="R70">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="S70">
         <v>2.68</v>
@@ -18863,10 +18863,10 @@
         <v>1.01</v>
       </c>
       <c r="V70">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W70">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -19060,7 +19060,7 @@
         <v>2.38</v>
       </c>
       <c r="G71">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="H71">
         <v>2.62</v>
@@ -19087,7 +19087,7 @@
         <v>1.3</v>
       </c>
       <c r="P71">
-        <v>1.96</v>
+        <v>1.34</v>
       </c>
       <c r="Q71">
         <v>1.85</v>
@@ -19108,7 +19108,7 @@
         <v>1.48</v>
       </c>
       <c r="W71">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -19299,19 +19299,19 @@
         <v>460</v>
       </c>
       <c r="F72">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H72">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="I72">
         <v>3.4</v>
       </c>
       <c r="J72">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="K72">
         <v>3.45</v>
@@ -19329,13 +19329,13 @@
         <v>1.33</v>
       </c>
       <c r="P72">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q72">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R72">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S72">
         <v>3.4</v>
@@ -19350,7 +19350,7 @@
         <v>1.42</v>
       </c>
       <c r="W72">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X72">
         <v>1000</v>
@@ -19783,7 +19783,7 @@
         <v>462</v>
       </c>
       <c r="F74">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G74">
         <v>2.46</v>
@@ -19795,10 +19795,10 @@
         <v>4.2</v>
       </c>
       <c r="J74">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="K74">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19819,10 +19819,10 @@
         <v>2.08</v>
       </c>
       <c r="R74">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S74">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="T74">
         <v>1.01</v>
@@ -19834,7 +19834,7 @@
         <v>1.31</v>
       </c>
       <c r="W74">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X74">
         <v>1000</v>
@@ -20031,13 +20031,13 @@
         <v>110</v>
       </c>
       <c r="H75">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I75">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="J75">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="K75">
         <v>410</v>
@@ -20073,10 +20073,10 @@
         <v>1.01</v>
       </c>
       <c r="V75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W75">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
         <v>1000</v>
@@ -20273,7 +20273,7 @@
         <v>3.45</v>
       </c>
       <c r="H76">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I76">
         <v>3.05</v>
@@ -20509,28 +20509,28 @@
         <v>465</v>
       </c>
       <c r="F77">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G77">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H77">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="I77">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="J77">
         <v>3.15</v>
       </c>
       <c r="K77">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L77">
         <v>1.01</v>
       </c>
       <c r="M77">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N77">
         <v>3.15</v>
@@ -20557,10 +20557,10 @@
         <v>1.01</v>
       </c>
       <c r="V77">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W77">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -20999,10 +20999,10 @@
         <v>2.9</v>
       </c>
       <c r="H79">
+        <v>2.7</v>
+      </c>
+      <c r="I79">
         <v>2.72</v>
-      </c>
-      <c r="I79">
-        <v>2.74</v>
       </c>
       <c r="J79">
         <v>3.5</v>
@@ -21017,7 +21017,7 @@
         <v>1.06</v>
       </c>
       <c r="N79">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O79">
         <v>1.29</v>
@@ -21026,25 +21026,25 @@
         <v>2.1</v>
       </c>
       <c r="Q79">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R79">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S79">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T79">
         <v>1.7</v>
       </c>
       <c r="U79">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V79">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W79">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X79">
         <v>16</v>
@@ -21053,7 +21053,7 @@
         <v>12.5</v>
       </c>
       <c r="Z79">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA79">
         <v>40</v>
@@ -21125,7 +21125,7 @@
         <v>25</v>
       </c>
       <c r="AX79">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY79">
         <v>11.5</v>
@@ -21313,7 +21313,7 @@
         <v>44</v>
       </c>
       <c r="AF80">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG80">
         <v>12.5</v>
@@ -21328,7 +21328,7 @@
         <v>40</v>
       </c>
       <c r="AK80">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL80">
         <v>55</v>
@@ -21379,7 +21379,7 @@
         <v>55</v>
       </c>
       <c r="BB80">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC80">
         <v>30</v>
@@ -21480,7 +21480,7 @@
         <v>3.2</v>
       </c>
       <c r="G81">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H81">
         <v>2.4</v>
@@ -21725,7 +21725,7 @@
         <v>3.55</v>
       </c>
       <c r="H82">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I82">
         <v>2.22</v>
@@ -21743,13 +21743,13 @@
         <v>1.05</v>
       </c>
       <c r="N82">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O82">
         <v>1.24</v>
       </c>
       <c r="P82">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q82">
         <v>1.74</v>
@@ -21767,7 +21767,7 @@
         <v>2.52</v>
       </c>
       <c r="V82">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W82">
         <v>1.39</v>
@@ -21815,7 +21815,7 @@
         <v>36</v>
       </c>
       <c r="AL82">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM82">
         <v>65</v>
@@ -21985,7 +21985,7 @@
         <v>1.08</v>
       </c>
       <c r="N83">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O83">
         <v>1.29</v>
@@ -22212,7 +22212,7 @@
         <v>3.75</v>
       </c>
       <c r="I84">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J84">
         <v>2.86</v>
@@ -22224,16 +22224,16 @@
         <v>1.47</v>
       </c>
       <c r="M84">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N84">
         <v>2.74</v>
       </c>
       <c r="O84">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P84">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q84">
         <v>2.46</v>
@@ -22242,7 +22242,7 @@
         <v>1.18</v>
       </c>
       <c r="S84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T84">
         <v>1.92</v>
@@ -22514,7 +22514,7 @@
         <v>14.5</v>
       </c>
       <c r="AC85">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD85">
         <v>12</v>
@@ -22696,10 +22696,10 @@
         <v>2.5</v>
       </c>
       <c r="I86">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="J86">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K86">
         <v>4.3</v>
@@ -22711,19 +22711,19 @@
         <v>1.01</v>
       </c>
       <c r="N86">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="O86">
         <v>1.22</v>
       </c>
       <c r="P86">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q86">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R86">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="S86">
         <v>2.58</v>
@@ -22735,7 +22735,7 @@
         <v>1.01</v>
       </c>
       <c r="V86">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W86">
         <v>1.5</v>
@@ -23437,19 +23437,19 @@
         <v>1.05</v>
       </c>
       <c r="N89">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O89">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P89">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q89">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="R89">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S89">
         <v>3.5</v>
@@ -23667,7 +23667,7 @@
         <v>6.6</v>
       </c>
       <c r="J90">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="K90">
         <v>4.2</v>
@@ -23691,7 +23691,7 @@
         <v>1.8</v>
       </c>
       <c r="R90">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S90">
         <v>3.25</v>
@@ -23700,7 +23700,7 @@
         <v>1.01</v>
       </c>
       <c r="U90">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V90">
         <v>1.2</v>
@@ -24381,13 +24381,13 @@
         <v>481</v>
       </c>
       <c r="F93">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G93">
         <v>2.08</v>
       </c>
       <c r="H93">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I93">
         <v>110</v>
@@ -24429,10 +24429,10 @@
         <v>1.01</v>
       </c>
       <c r="V93">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W93">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X93">
         <v>1000</v>
@@ -24865,7 +24865,7 @@
         <v>483</v>
       </c>
       <c r="F95">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G95">
         <v>1.56</v>
@@ -24907,7 +24907,7 @@
         <v>2.28</v>
       </c>
       <c r="T95">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U95">
         <v>1.01</v>
@@ -25349,10 +25349,10 @@
         <v>485</v>
       </c>
       <c r="F97">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="G97">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="H97">
         <v>2.2</v>
@@ -25361,10 +25361,10 @@
         <v>2.32</v>
       </c>
       <c r="J97">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K97">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L97">
         <v>1.01</v>
@@ -25400,7 +25400,7 @@
         <v>1.75</v>
       </c>
       <c r="W97">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="X97">
         <v>1000</v>
@@ -25600,7 +25600,7 @@
         <v>3.15</v>
       </c>
       <c r="I98">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J98">
         <v>3.1</v>
@@ -25612,37 +25612,37 @@
         <v>1.01</v>
       </c>
       <c r="M98">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N98">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O98">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P98">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="Q98">
-        <v>2.28</v>
+        <v>1.42</v>
       </c>
       <c r="R98">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S98">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T98">
         <v>1.75</v>
       </c>
       <c r="U98">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W98">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X98">
         <v>13</v>
@@ -25678,7 +25678,7 @@
         <v>23</v>
       </c>
       <c r="AI98">
-        <v>760</v>
+        <v>670</v>
       </c>
       <c r="AJ98">
         <v>44</v>
@@ -25690,7 +25690,7 @@
         <v>60</v>
       </c>
       <c r="AM98">
-        <v>760</v>
+        <v>670</v>
       </c>
       <c r="AN98">
         <v>34</v>
@@ -25729,7 +25729,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ98">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA98">
         <v>4.5</v>
@@ -25833,7 +25833,7 @@
         <v>487</v>
       </c>
       <c r="F99">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G99">
         <v>2.8</v>
@@ -25842,13 +25842,13 @@
         <v>3.1</v>
       </c>
       <c r="I99">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J99">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="K99">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L99">
         <v>1.01</v>
@@ -25881,7 +25881,7 @@
         <v>1.01</v>
       </c>
       <c r="V99">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W99">
         <v>1.55</v>
@@ -26317,13 +26317,13 @@
         <v>489</v>
       </c>
       <c r="F101">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G101">
         <v>110</v>
       </c>
       <c r="H101">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I101">
         <v>110</v>
@@ -26365,10 +26365,10 @@
         <v>1.01</v>
       </c>
       <c r="V101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
         <v>1000</v>
@@ -26580,28 +26580,28 @@
         <v>1.01</v>
       </c>
       <c r="M102">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N102">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="O102">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P102">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q102">
+        <v>1.53</v>
+      </c>
+      <c r="R102">
+        <v>1.41</v>
+      </c>
+      <c r="S102">
+        <v>2.32</v>
+      </c>
+      <c r="T102">
         <v>1.62</v>
-      </c>
-      <c r="R102">
-        <v>1.56</v>
-      </c>
-      <c r="S102">
-        <v>2.58</v>
-      </c>
-      <c r="T102">
-        <v>1.51</v>
       </c>
       <c r="U102">
         <v>2.4</v>
@@ -26825,19 +26825,19 @@
         <v>1.01</v>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="O103">
         <v>1.06</v>
       </c>
       <c r="P103">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q103">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="R103">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S103">
         <v>1.06</v>
@@ -27043,10 +27043,10 @@
         <v>492</v>
       </c>
       <c r="F104">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G104">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H104">
         <v>1.32</v>
@@ -27094,7 +27094,7 @@
         <v>4</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X104">
         <v>38</v>
@@ -27121,7 +27121,7 @@
         <v>12.5</v>
       </c>
       <c r="AF104">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AG104">
         <v>40</v>
@@ -27145,13 +27145,13 @@
         <v>95</v>
       </c>
       <c r="AN104">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AO104">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AP104">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ104">
         <v>13</v>
@@ -27160,10 +27160,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT104">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU104">
         <v>13.5</v>
@@ -27187,7 +27187,7 @@
         <v>23</v>
       </c>
       <c r="BB104">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC104">
         <v>42</v>
@@ -27199,7 +27199,7 @@
         <v>38</v>
       </c>
       <c r="BF104">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BG104">
         <v>3.5</v>
@@ -27285,7 +27285,7 @@
         <v>493</v>
       </c>
       <c r="F105">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G105">
         <v>2.04</v>
@@ -27294,7 +27294,7 @@
         <v>4.9</v>
       </c>
       <c r="I105">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J105">
         <v>3.25</v>
@@ -27306,7 +27306,7 @@
         <v>1.01</v>
       </c>
       <c r="M105">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N105">
         <v>2.42</v>
@@ -27315,10 +27315,10 @@
         <v>1.54</v>
       </c>
       <c r="P105">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Q105">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R105">
         <v>1.17</v>
@@ -27333,7 +27333,7 @@
         <v>1.6</v>
       </c>
       <c r="V105">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W105">
         <v>1.96</v>
@@ -27784,7 +27784,7 @@
         <v>3.35</v>
       </c>
       <c r="K107">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L107">
         <v>1.01</v>
@@ -27805,7 +27805,7 @@
         <v>2.22</v>
       </c>
       <c r="R107">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S107">
         <v>1.01</v>
@@ -28265,7 +28265,7 @@
         <v>2.16</v>
       </c>
       <c r="J109">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K109">
         <v>3.9</v>
@@ -28495,7 +28495,7 @@
         <v>498</v>
       </c>
       <c r="F110">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G110">
         <v>1.87</v>
@@ -28510,7 +28510,7 @@
         <v>4</v>
       </c>
       <c r="K110">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L110">
         <v>1.01</v>
@@ -28519,7 +28519,7 @@
         <v>1.01</v>
       </c>
       <c r="N110">
-        <v>2.76</v>
+        <v>5.3</v>
       </c>
       <c r="O110">
         <v>1.12</v>
@@ -28603,7 +28603,7 @@
         <v>1000</v>
       </c>
       <c r="AP110">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ110">
         <v>1.01</v>
@@ -28764,16 +28764,16 @@
         <v>1.01</v>
       </c>
       <c r="O111">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P111">
         <v>1.25</v>
       </c>
       <c r="Q111">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R111">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S111">
         <v>2.42</v>
@@ -28782,7 +28782,7 @@
         <v>1.01</v>
       </c>
       <c r="U111">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V111">
         <v>1.45</v>
@@ -28988,7 +28988,7 @@
         <v>2.04</v>
       </c>
       <c r="I112">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J112">
         <v>3.4</v>
@@ -29221,19 +29221,19 @@
         <v>501</v>
       </c>
       <c r="F113">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G113">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H113">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I113">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J113">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K113">
         <v>4.4</v>
@@ -29242,37 +29242,37 @@
         <v>1.22</v>
       </c>
       <c r="M113">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N113">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="O113">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P113">
-        <v>1.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q113">
         <v>1.48</v>
       </c>
       <c r="R113">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S113">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="T113">
         <v>1.44</v>
       </c>
       <c r="U113">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V113">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W113">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="X113">
         <v>32</v>
@@ -29311,7 +29311,7 @@
         <v>32</v>
       </c>
       <c r="AJ113">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK113">
         <v>19.5</v>
@@ -29323,7 +29323,7 @@
         <v>48</v>
       </c>
       <c r="AN113">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO113">
         <v>16.5</v>
@@ -29335,7 +29335,7 @@
         <v>21</v>
       </c>
       <c r="AR113">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS113">
         <v>46</v>
@@ -29344,13 +29344,13 @@
         <v>16</v>
       </c>
       <c r="AU113">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV113">
         <v>13.5</v>
       </c>
       <c r="AW113">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX113">
         <v>17</v>
@@ -29750,7 +29750,7 @@
         <v>1.01</v>
       </c>
       <c r="U115">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V115">
         <v>1.11</v>
@@ -29986,7 +29986,7 @@
         <v>1.83</v>
       </c>
       <c r="S116">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T116">
         <v>1.38</v>
@@ -30189,7 +30189,7 @@
         <v>505</v>
       </c>
       <c r="F117">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G117">
         <v>110</v>
@@ -30201,7 +30201,7 @@
         <v>110</v>
       </c>
       <c r="J117">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K117">
         <v>190</v>
@@ -30237,7 +30237,7 @@
         <v>1.01</v>
       </c>
       <c r="V117">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W117">
         <v>1.06</v>
@@ -30431,7 +30431,7 @@
         <v>506</v>
       </c>
       <c r="F118">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G118">
         <v>380</v>
@@ -30443,7 +30443,7 @@
         <v>1000</v>
       </c>
       <c r="J118">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="K118">
         <v>210</v>
@@ -30479,7 +30479,7 @@
         <v>1.01</v>
       </c>
       <c r="V118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W118">
         <v>1.02</v>
@@ -30685,7 +30685,7 @@
         <v>110</v>
       </c>
       <c r="J119">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K119">
         <v>300</v>
@@ -30703,7 +30703,7 @@
         <v>1.01</v>
       </c>
       <c r="P119">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q119">
         <v>1.01</v>
@@ -30712,7 +30712,7 @@
         <v>1.07</v>
       </c>
       <c r="S119">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="T119">
         <v>1.01</v>
@@ -30721,10 +30721,10 @@
         <v>1.01</v>
       </c>
       <c r="V119">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W119">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1000</v>
@@ -30918,16 +30918,16 @@
         <v>2.1</v>
       </c>
       <c r="G120">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="H120">
         <v>2.98</v>
       </c>
       <c r="I120">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J120">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K120">
         <v>5.4</v>
@@ -30963,10 +30963,10 @@
         <v>1.01</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W120">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="X120">
         <v>1000</v>
@@ -31190,13 +31190,13 @@
         <v>2.28</v>
       </c>
       <c r="Q121">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R121">
         <v>1.5</v>
       </c>
       <c r="S121">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T121">
         <v>1.69</v>
@@ -31211,7 +31211,7 @@
         <v>1.3</v>
       </c>
       <c r="X121">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y121">
         <v>11.5</v>
@@ -31232,7 +31232,7 @@
         <v>10.5</v>
       </c>
       <c r="AE121">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF121">
         <v>34</v>
@@ -31408,7 +31408,7 @@
         <v>5.4</v>
       </c>
       <c r="I122">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J122">
         <v>3.7</v>
@@ -31423,22 +31423,22 @@
         <v>1.07</v>
       </c>
       <c r="N122">
-        <v>3.65</v>
+        <v>1.58</v>
       </c>
       <c r="O122">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P122">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="Q122">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="R122">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S122">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="T122">
         <v>1.01</v>
@@ -31453,7 +31453,7 @@
         <v>2.18</v>
       </c>
       <c r="X122">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y122">
         <v>21</v>
@@ -31462,13 +31462,13 @@
         <v>46</v>
       </c>
       <c r="AA122">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="AB122">
         <v>9.4</v>
       </c>
       <c r="AC122">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD122">
         <v>25</v>
@@ -31498,7 +31498,7 @@
         <v>44</v>
       </c>
       <c r="AM122">
-        <v>850</v>
+        <v>760</v>
       </c>
       <c r="AN122">
         <v>13.5</v>
@@ -31513,10 +31513,10 @@
         <v>16</v>
       </c>
       <c r="AR122">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AS122">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT122">
         <v>7</v>
@@ -31528,7 +31528,7 @@
         <v>18.5</v>
       </c>
       <c r="AW122">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX122">
         <v>8.199999999999999</v>
@@ -31540,7 +31540,7 @@
         <v>15</v>
       </c>
       <c r="BA122">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB122">
         <v>14</v>
@@ -31549,16 +31549,16 @@
         <v>14.5</v>
       </c>
       <c r="BD122">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE122">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF122">
         <v>9</v>
       </c>
       <c r="BG122">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH122">
         <v>1000</v>
@@ -31883,7 +31883,7 @@
         <v>512</v>
       </c>
       <c r="F124">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G124">
         <v>1.7</v>
@@ -31907,13 +31907,13 @@
         <v>1.01</v>
       </c>
       <c r="N124">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="O124">
         <v>1.17</v>
       </c>
       <c r="P124">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q124">
         <v>1.47</v>
@@ -32170,7 +32170,7 @@
         <v>1.51</v>
       </c>
       <c r="U125">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V125">
         <v>1.37</v>
@@ -32379,7 +32379,7 @@
         <v>110</v>
       </c>
       <c r="J126">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K126">
         <v>210</v>
@@ -32415,10 +32415,10 @@
         <v>1.01</v>
       </c>
       <c r="V126">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1000</v>
@@ -32615,7 +32615,7 @@
         <v>2.84</v>
       </c>
       <c r="H127">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I127">
         <v>3.1</v>
@@ -32642,7 +32642,7 @@
         <v>1.87</v>
       </c>
       <c r="Q127">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R127">
         <v>1.32</v>
@@ -32651,10 +32651,10 @@
         <v>3.25</v>
       </c>
       <c r="T127">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U127">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V127">
         <v>1.47</v>
@@ -32863,7 +32863,7 @@
         <v>110</v>
       </c>
       <c r="J128">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K128">
         <v>210</v>
@@ -32899,10 +32899,10 @@
         <v>1.01</v>
       </c>
       <c r="V128">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W128">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X128">
         <v>1000</v>
@@ -33093,16 +33093,16 @@
         <v>517</v>
       </c>
       <c r="F129">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G129">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H129">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I129">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J129">
         <v>4.1</v>
@@ -33132,7 +33132,7 @@
         <v>1.5</v>
       </c>
       <c r="S129">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T129">
         <v>1.76</v>
@@ -33141,19 +33141,19 @@
         <v>2.28</v>
       </c>
       <c r="V129">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W129">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X129">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y129">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z129">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA129">
         <v>120</v>
@@ -33165,10 +33165,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD129">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE129">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF129">
         <v>11</v>
@@ -33183,7 +33183,7 @@
         <v>60</v>
       </c>
       <c r="AJ129">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK129">
         <v>16</v>
@@ -33192,25 +33192,25 @@
         <v>30</v>
       </c>
       <c r="AM129">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN129">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO129">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP129">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ129">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AR129">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS129">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AT129">
         <v>9.800000000000001</v>
@@ -33219,31 +33219,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV129">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW129">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AX129">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY129">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ129">
         <v>17</v>
       </c>
       <c r="BA129">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB129">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC129">
         <v>15.5</v>
       </c>
       <c r="BD129">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE129">
         <v>65</v>
@@ -33252,7 +33252,7 @@
         <v>8.6</v>
       </c>
       <c r="BG129">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BH129">
         <v>3.95</v>
@@ -33344,7 +33344,7 @@
         <v>6.4</v>
       </c>
       <c r="I130">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="J130">
         <v>4.1</v>
@@ -33362,7 +33362,7 @@
         <v>1.85</v>
       </c>
       <c r="O130">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P130">
         <v>1.85</v>
@@ -33601,19 +33601,19 @@
         <v>1.01</v>
       </c>
       <c r="N131">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O131">
         <v>1.14</v>
       </c>
       <c r="P131">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q131">
         <v>1.46</v>
       </c>
       <c r="R131">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S131">
         <v>2.2</v>
@@ -33846,7 +33846,7 @@
         <v>2.44</v>
       </c>
       <c r="O132">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P132">
         <v>1.56</v>
@@ -33855,7 +33855,7 @@
         <v>2.04</v>
       </c>
       <c r="R132">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S132">
         <v>4</v>
@@ -34070,7 +34070,7 @@
         <v>1.21</v>
       </c>
       <c r="I133">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="J133">
         <v>5.1</v>
@@ -34109,7 +34109,7 @@
         <v>1.01</v>
       </c>
       <c r="V133">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="W133">
         <v>1.01</v>
@@ -34811,7 +34811,7 @@
         <v>1.01</v>
       </c>
       <c r="N136">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="O136">
         <v>1.2</v>
@@ -34823,7 +34823,7 @@
         <v>1.56</v>
       </c>
       <c r="R136">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S136">
         <v>2.46</v>
@@ -34832,13 +34832,13 @@
         <v>1.01</v>
       </c>
       <c r="U136">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V136">
         <v>1.17</v>
       </c>
       <c r="W136">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X136">
         <v>1000</v>
@@ -35513,22 +35513,22 @@
         <v>527</v>
       </c>
       <c r="F139">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="G139">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="H139">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="I139">
-        <v>110</v>
+        <v>17.5</v>
       </c>
       <c r="J139">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="K139">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L139">
         <v>1.01</v>
@@ -35537,22 +35537,22 @@
         <v>1.01</v>
       </c>
       <c r="N139">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="O139">
         <v>1.14</v>
       </c>
       <c r="P139">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="Q139">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="R139">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="S139">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="T139">
         <v>1.01</v>
@@ -35561,118 +35561,118 @@
         <v>1.01</v>
       </c>
       <c r="V139">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W139">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="X139">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="Y139">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="Z139">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AA139">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB139">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AC139">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AD139">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE139">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AF139">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG139">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH139">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI139">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ139">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK139">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL139">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM139">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN139">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO139">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP139">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ139">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AR139">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="AS139">
-        <v>1.01</v>
+        <v>320</v>
       </c>
       <c r="AT139">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU139">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV139">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AW139">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="AX139">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY139">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ139">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA139">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB139">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC139">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD139">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE139">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF139">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BG139">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH139">
         <v>1000</v>
@@ -35997,7 +35997,7 @@
         <v>529</v>
       </c>
       <c r="F141">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G141">
         <v>3.9</v>
@@ -36006,37 +36006,37 @@
         <v>2.36</v>
       </c>
       <c r="I141">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J141">
         <v>2.98</v>
       </c>
       <c r="K141">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L141">
         <v>1.44</v>
       </c>
       <c r="M141">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N141">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="O141">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P141">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q141">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R141">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S141">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="T141">
         <v>1.01</v>
@@ -36239,10 +36239,10 @@
         <v>530</v>
       </c>
       <c r="F142">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G142">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H142">
         <v>2.14</v>
@@ -36251,10 +36251,10 @@
         <v>2.38</v>
       </c>
       <c r="J142">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K142">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L142">
         <v>1.01</v>
@@ -36290,7 +36290,7 @@
         <v>1.72</v>
       </c>
       <c r="W142">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X142">
         <v>1000</v>
@@ -36493,7 +36493,7 @@
         <v>110</v>
       </c>
       <c r="J143">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K143">
         <v>300</v>
@@ -36753,7 +36753,7 @@
         <v>1.34</v>
       </c>
       <c r="P144">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q144">
         <v>2.02</v>
@@ -36762,7 +36762,7 @@
         <v>1.36</v>
       </c>
       <c r="S144">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T144">
         <v>1.78</v>
@@ -36783,7 +36783,7 @@
         <v>12.5</v>
       </c>
       <c r="Z144">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA144">
         <v>55</v>
@@ -36834,7 +36834,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ144">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR144">
         <v>20</v>
@@ -36965,7 +36965,7 @@
         <v>533</v>
       </c>
       <c r="F145">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="G145">
         <v>1000</v>
@@ -36980,7 +36980,7 @@
         <v>1.1</v>
       </c>
       <c r="K145">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L145">
         <v>1.01</v>
@@ -37207,7 +37207,7 @@
         <v>534</v>
       </c>
       <c r="F146">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G146">
         <v>2.46</v>
@@ -37216,7 +37216,7 @@
         <v>3.35</v>
       </c>
       <c r="I146">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J146">
         <v>3.05</v>
@@ -37473,28 +37473,28 @@
         <v>1.01</v>
       </c>
       <c r="N147">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="O147">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P147">
         <v>2.1</v>
       </c>
       <c r="Q147">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="R147">
         <v>1.46</v>
       </c>
       <c r="S147">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T147">
         <v>1.01</v>
       </c>
       <c r="U147">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V147">
         <v>1.41</v>
@@ -37691,10 +37691,10 @@
         <v>536</v>
       </c>
       <c r="F148">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G148">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H148">
         <v>3.75</v>
@@ -37703,16 +37703,16 @@
         <v>3.85</v>
       </c>
       <c r="J148">
+        <v>3.1</v>
+      </c>
+      <c r="K148">
         <v>3.15</v>
-      </c>
-      <c r="K148">
-        <v>3.2</v>
       </c>
       <c r="L148">
         <v>1.58</v>
       </c>
       <c r="M148">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N148">
         <v>2.76</v>
@@ -37730,7 +37730,7 @@
         <v>1.21</v>
       </c>
       <c r="S148">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T148">
         <v>2.14</v>
@@ -37742,7 +37742,7 @@
         <v>1.35</v>
       </c>
       <c r="W148">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X148">
         <v>9</v>
@@ -37766,7 +37766,7 @@
         <v>16.5</v>
       </c>
       <c r="AE148">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF148">
         <v>13</v>
@@ -37808,7 +37808,7 @@
         <v>21</v>
       </c>
       <c r="AS148">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AT148">
         <v>7</v>
@@ -37850,7 +37850,7 @@
         <v>29</v>
       </c>
       <c r="BG148">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="BH148">
         <v>1000</v>
@@ -38175,19 +38175,19 @@
         <v>538</v>
       </c>
       <c r="F150">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="G150">
         <v>2.78</v>
       </c>
       <c r="H150">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I150">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J150">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="K150">
         <v>3.2</v>
@@ -38202,19 +38202,19 @@
         <v>2.66</v>
       </c>
       <c r="O150">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="P150">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q150">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R150">
         <v>1.2</v>
       </c>
       <c r="S150">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T150">
         <v>1.01</v>
@@ -38223,7 +38223,7 @@
         <v>1.79</v>
       </c>
       <c r="V150">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W150">
         <v>1.56</v>
@@ -38283,7 +38283,7 @@
         <v>1000</v>
       </c>
       <c r="AP150">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ150">
         <v>8.6</v>
@@ -39167,13 +39167,13 @@
         <v>1.01</v>
       </c>
       <c r="N154">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="O154">
         <v>1.25</v>
       </c>
       <c r="P154">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q154">
         <v>1.25</v>
@@ -39418,7 +39418,7 @@
         <v>3.2</v>
       </c>
       <c r="Q155">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="R155">
         <v>2.08</v>
@@ -39427,7 +39427,7 @@
         <v>1.68</v>
       </c>
       <c r="T155">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="U155">
         <v>1.01</v>
@@ -39869,7 +39869,7 @@
         <v>545</v>
       </c>
       <c r="F157">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G157">
         <v>1.59</v>
@@ -39878,13 +39878,13 @@
         <v>7.4</v>
       </c>
       <c r="I157">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="J157">
         <v>4.2</v>
       </c>
       <c r="K157">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L157">
         <v>1.01</v>
@@ -39893,16 +39893,16 @@
         <v>1.03</v>
       </c>
       <c r="N157">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="O157">
+        <v>1.32</v>
+      </c>
+      <c r="P157">
+        <v>1.73</v>
+      </c>
+      <c r="Q157">
         <v>1.33</v>
-      </c>
-      <c r="P157">
-        <v>1.81</v>
-      </c>
-      <c r="Q157">
-        <v>1.34</v>
       </c>
       <c r="R157">
         <v>1.26</v>
@@ -39911,10 +39911,10 @@
         <v>3.55</v>
       </c>
       <c r="T157">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U157">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V157">
         <v>1.13</v>
@@ -39923,112 +39923,112 @@
         <v>2.68</v>
       </c>
       <c r="X157">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y157">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z157">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA157">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB157">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC157">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD157">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE157">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF157">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG157">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH157">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI157">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ157">
+        <v>1000</v>
+      </c>
+      <c r="AK157">
+        <v>1000</v>
+      </c>
+      <c r="AL157">
+        <v>1000</v>
+      </c>
+      <c r="AM157">
+        <v>1000</v>
+      </c>
+      <c r="AN157">
+        <v>1000</v>
+      </c>
+      <c r="AO157">
+        <v>1000</v>
+      </c>
+      <c r="AP157">
+        <v>10.5</v>
+      </c>
+      <c r="AQ157">
         <v>16.5</v>
       </c>
-      <c r="AK157">
+      <c r="AR157">
+        <v>38</v>
+      </c>
+      <c r="AS157">
+        <v>5.4</v>
+      </c>
+      <c r="AT157">
+        <v>6</v>
+      </c>
+      <c r="AU157">
+        <v>8</v>
+      </c>
+      <c r="AV157">
         <v>21</v>
       </c>
-      <c r="AL157">
-        <v>55</v>
-      </c>
-      <c r="AM157">
-        <v>210</v>
-      </c>
-      <c r="AN157">
-        <v>12</v>
-      </c>
-      <c r="AO157">
-        <v>250</v>
-      </c>
-      <c r="AP157">
-        <v>11.5</v>
-      </c>
-      <c r="AQ157">
-        <v>18</v>
-      </c>
-      <c r="AR157">
-        <v>5</v>
-      </c>
-      <c r="AS157">
+      <c r="AW157">
         <v>5.3</v>
       </c>
-      <c r="AT157">
-        <v>6.2</v>
-      </c>
-      <c r="AU157">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV157">
-        <v>4.6</v>
-      </c>
-      <c r="AW157">
-        <v>5.2</v>
-      </c>
       <c r="AX157">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY157">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ157">
         <v>21</v>
       </c>
       <c r="BA157">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB157">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC157">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BD157">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="BE157">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF157">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG157">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH157">
         <v>1000</v>
@@ -40374,10 +40374,10 @@
         <v>1.01</v>
       </c>
       <c r="M159">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N159">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O159">
         <v>1.34</v>
@@ -40386,10 +40386,10 @@
         <v>1.81</v>
       </c>
       <c r="Q159">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R159">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S159">
         <v>2.92</v>
@@ -40634,7 +40634,7 @@
         <v>1.36</v>
       </c>
       <c r="S160">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T160">
         <v>1.01</v>
@@ -41079,10 +41079,10 @@
         <v>550</v>
       </c>
       <c r="F162">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G162">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H162">
         <v>1.73</v>
@@ -41121,7 +41121,7 @@
         <v>2.5</v>
       </c>
       <c r="T162">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U162">
         <v>1.01</v>
@@ -41321,22 +41321,22 @@
         <v>551</v>
       </c>
       <c r="F163">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="G163">
-        <v>3.35</v>
+        <v>18.5</v>
       </c>
       <c r="H163">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="I163">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J163">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="K163">
-        <v>3.85</v>
+        <v>210</v>
       </c>
       <c r="L163">
         <v>1.01</v>
@@ -41363,16 +41363,16 @@
         <v>3.25</v>
       </c>
       <c r="T163">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U163">
         <v>1.01</v>
       </c>
       <c r="V163">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W163">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X163">
         <v>1000</v>
@@ -41805,7 +41805,7 @@
         <v>553</v>
       </c>
       <c r="F165">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G165">
         <v>1.75</v>
@@ -41814,13 +41814,13 @@
         <v>6.4</v>
       </c>
       <c r="I165">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J165">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K165">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="L165">
         <v>1.01</v>
@@ -41838,7 +41838,7 @@
         <v>1.43</v>
       </c>
       <c r="Q165">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="R165">
         <v>1.14</v>
@@ -41853,7 +41853,7 @@
         <v>1.01</v>
       </c>
       <c r="V165">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W165">
         <v>2.32</v>
@@ -42062,7 +42062,7 @@
         <v>3.65</v>
       </c>
       <c r="K166">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L166">
         <v>1.3</v>
@@ -42071,7 +42071,7 @@
         <v>1.01</v>
       </c>
       <c r="N166">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="O166">
         <v>1.3</v>
@@ -42080,7 +42080,7 @@
         <v>1.9</v>
       </c>
       <c r="Q166">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R166">
         <v>1.33</v>
@@ -42298,10 +42298,10 @@
         <v>3.3</v>
       </c>
       <c r="I167">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J167">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K167">
         <v>7.8</v>
@@ -42325,13 +42325,13 @@
         <v>1.46</v>
       </c>
       <c r="R167">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S167">
         <v>2.12</v>
       </c>
       <c r="T167">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U167">
         <v>1.01</v>
@@ -42821,7 +42821,7 @@
         <v>1.01</v>
       </c>
       <c r="V169">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W169">
         <v>1.02</v>
@@ -43018,7 +43018,7 @@
         <v>1.82</v>
       </c>
       <c r="G170">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="H170">
         <v>3.3</v>
@@ -43066,7 +43066,7 @@
         <v>1.25</v>
       </c>
       <c r="W170">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="X170">
         <v>1000</v>
@@ -43547,10 +43547,10 @@
         <v>1.01</v>
       </c>
       <c r="V172">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W172">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X172">
         <v>1000</v>
@@ -43741,7 +43741,7 @@
         <v>561</v>
       </c>
       <c r="F173">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G173">
         <v>8.800000000000001</v>
@@ -43750,7 +43750,7 @@
         <v>1.55</v>
       </c>
       <c r="I173">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="J173">
         <v>3.6</v>
@@ -43789,7 +43789,7 @@
         <v>1.01</v>
       </c>
       <c r="V173">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="W173">
         <v>1.13</v>
@@ -43986,13 +43986,13 @@
         <v>2.28</v>
       </c>
       <c r="G174">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H174">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I174">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J174">
         <v>3.2</v>
@@ -44007,7 +44007,7 @@
         <v>1.08</v>
       </c>
       <c r="N174">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O174">
         <v>1.35</v>
@@ -44016,28 +44016,28 @@
         <v>1.83</v>
       </c>
       <c r="Q174">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R174">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S174">
         <v>3.6</v>
       </c>
       <c r="T174">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="U174">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V174">
         <v>1.36</v>
       </c>
       <c r="W174">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X174">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y174">
         <v>13.5</v>
@@ -44046,19 +44046,19 @@
         <v>25</v>
       </c>
       <c r="AA174">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB174">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC174">
         <v>8</v>
       </c>
       <c r="AD174">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE174">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF174">
         <v>15</v>
@@ -44073,10 +44073,10 @@
         <v>60</v>
       </c>
       <c r="AJ174">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK174">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL174">
         <v>42</v>
@@ -44085,7 +44085,7 @@
         <v>110</v>
       </c>
       <c r="AN174">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO174">
         <v>50</v>
@@ -44109,13 +44109,13 @@
         <v>6.8</v>
       </c>
       <c r="AV174">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW174">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX174">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY174">
         <v>9.800000000000001</v>
@@ -44124,10 +44124,10 @@
         <v>15.5</v>
       </c>
       <c r="BA174">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BB174">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC174">
         <v>22</v>
@@ -44136,10 +44136,10 @@
         <v>34</v>
       </c>
       <c r="BE174">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF174">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG174">
         <v>32</v>
@@ -44228,19 +44228,19 @@
         <v>1.54</v>
       </c>
       <c r="G175">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="H175">
-        <v>5.3</v>
+        <v>2.82</v>
       </c>
       <c r="I175">
         <v>10.5</v>
       </c>
       <c r="J175">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K175">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="L175">
         <v>1.01</v>
@@ -44249,19 +44249,19 @@
         <v>1.01</v>
       </c>
       <c r="N175">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="O175">
         <v>1.32</v>
       </c>
       <c r="P175">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q175">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="R175">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S175">
         <v>3.05</v>
@@ -44273,10 +44273,10 @@
         <v>1.01</v>
       </c>
       <c r="V175">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W175">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X175">
         <v>1000</v>
@@ -44470,7 +44470,7 @@
         <v>1.84</v>
       </c>
       <c r="G176">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H176">
         <v>4.3</v>
@@ -44518,7 +44518,7 @@
         <v>1.27</v>
       </c>
       <c r="W176">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X176">
         <v>22</v>
@@ -44584,7 +44584,7 @@
         <v>32</v>
       </c>
       <c r="AS176">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT176">
         <v>10.5</v>
@@ -44608,7 +44608,7 @@
         <v>15.5</v>
       </c>
       <c r="BA176">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="BB176">
         <v>18</v>
@@ -44617,10 +44617,10 @@
         <v>16</v>
       </c>
       <c r="BD176">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BE176">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="BF176">
         <v>8.4</v>
@@ -44718,7 +44718,7 @@
         <v>3.95</v>
       </c>
       <c r="I177">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J177">
         <v>3.45</v>
@@ -44739,7 +44739,7 @@
         <v>1.4</v>
       </c>
       <c r="P177">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q177">
         <v>2.18</v>
@@ -44769,13 +44769,13 @@
         <v>13</v>
       </c>
       <c r="Z177">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA177">
         <v>85</v>
       </c>
       <c r="AB177">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC177">
         <v>8.199999999999999</v>
@@ -44829,7 +44829,7 @@
         <v>65</v>
       </c>
       <c r="AT177">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU177">
         <v>7.8</v>
@@ -44880,7 +44880,7 @@
         <v>10.5</v>
       </c>
       <c r="BK177">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BL177">
         <v>990</v>
@@ -44898,7 +44898,7 @@
         <v>17</v>
       </c>
       <c r="BQ177">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR177">
         <v>34</v>
@@ -44910,7 +44910,7 @@
         <v>7</v>
       </c>
       <c r="BU177">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV177">
         <v>36</v>
@@ -44975,19 +44975,19 @@
         <v>1.01</v>
       </c>
       <c r="N178">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="O178">
         <v>1.35</v>
       </c>
       <c r="P178">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Q178">
         <v>1.35</v>
       </c>
       <c r="R178">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S178">
         <v>1.35</v>
@@ -45498,7 +45498,7 @@
         <v>25</v>
       </c>
       <c r="AA180">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB180">
         <v>8</v>
@@ -45534,7 +45534,7 @@
         <v>55</v>
       </c>
       <c r="AM180">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN180">
         <v>30</v>
@@ -45576,7 +45576,7 @@
         <v>20</v>
       </c>
       <c r="BA180">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BB180">
         <v>30</v>
@@ -45588,7 +45588,7 @@
         <v>48</v>
       </c>
       <c r="BE180">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="BF180">
         <v>26</v>
@@ -45713,10 +45713,10 @@
         <v>1.48</v>
       </c>
       <c r="R181">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S181">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="T181">
         <v>1.01</v>
@@ -45919,13 +45919,13 @@
         <v>570</v>
       </c>
       <c r="F182">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G182">
         <v>3.9</v>
       </c>
       <c r="H182">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I182">
         <v>2.94</v>
@@ -45934,13 +45934,13 @@
         <v>2.74</v>
       </c>
       <c r="K182">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="L182">
         <v>1.01</v>
       </c>
       <c r="M182">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N182">
         <v>2.38</v>
@@ -46188,10 +46188,10 @@
         <v>2.9</v>
       </c>
       <c r="O183">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P183">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q183">
         <v>1.96</v>
@@ -46406,7 +46406,7 @@
         <v>1.92</v>
       </c>
       <c r="G184">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H184">
         <v>4.2</v>
@@ -46418,7 +46418,7 @@
         <v>3.4</v>
       </c>
       <c r="K184">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L184">
         <v>1.01</v>
@@ -46433,7 +46433,7 @@
         <v>1.35</v>
       </c>
       <c r="P184">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="Q184">
         <v>2.08</v>
@@ -46454,7 +46454,7 @@
         <v>1.26</v>
       </c>
       <c r="W184">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="X184">
         <v>1000</v>
@@ -46666,10 +46666,10 @@
         <v>1.01</v>
       </c>
       <c r="M185">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N185">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="O185">
         <v>1.22</v>
@@ -46678,7 +46678,7 @@
         <v>1.38</v>
       </c>
       <c r="Q185">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="R185">
         <v>1.38</v>
@@ -46714,7 +46714,7 @@
         <v>1000</v>
       </c>
       <c r="AC185">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD185">
         <v>1000</v>
@@ -46753,58 +46753,58 @@
         <v>1000</v>
       </c>
       <c r="AP185">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="AQ185">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="AR185">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="AS185">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="AT185">
-        <v>18.5</v>
+        <v>1.1</v>
       </c>
       <c r="AU185">
         <v>8.800000000000001</v>
       </c>
       <c r="AV185">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="AW185">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="AX185">
-        <v>40</v>
+        <v>1.1</v>
       </c>
       <c r="AY185">
-        <v>19.5</v>
+        <v>1.1</v>
       </c>
       <c r="AZ185">
-        <v>18</v>
+        <v>1.1</v>
       </c>
       <c r="BA185">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="BB185">
-        <v>100</v>
+        <v>1.1</v>
       </c>
       <c r="BC185">
-        <v>60</v>
+        <v>1.1</v>
       </c>
       <c r="BD185">
-        <v>55</v>
+        <v>1.1</v>
       </c>
       <c r="BE185">
-        <v>80</v>
+        <v>1.1</v>
       </c>
       <c r="BF185">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG185">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH185">
         <v>1000</v>
@@ -46917,7 +46917,7 @@
         <v>1.23</v>
       </c>
       <c r="P186">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q186">
         <v>1.6</v>
@@ -46926,7 +46926,7 @@
         <v>1.44</v>
       </c>
       <c r="S186">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="T186">
         <v>1.01</v>
@@ -47156,10 +47156,10 @@
         <v>1.01</v>
       </c>
       <c r="O187">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P187">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q187">
         <v>2.12</v>
@@ -47168,7 +47168,7 @@
         <v>1.22</v>
       </c>
       <c r="S187">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T187">
         <v>1.01</v>
@@ -47622,7 +47622,7 @@
         <v>1.32</v>
       </c>
       <c r="I189">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J189">
         <v>3.3</v>
@@ -47643,16 +47643,16 @@
         <v>1.28</v>
       </c>
       <c r="P189">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Q189">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R189">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="S189">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="T189">
         <v>1.01</v>
@@ -47661,7 +47661,7 @@
         <v>1.01</v>
       </c>
       <c r="V189">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W189">
         <v>1.01</v>
@@ -47879,22 +47879,22 @@
         <v>1.01</v>
       </c>
       <c r="N190">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="O190">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P190">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="Q190">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="R190">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S190">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="T190">
         <v>1.61</v>
@@ -47933,10 +47933,10 @@
         <v>18</v>
       </c>
       <c r="AF190">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AG190">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AH190">
         <v>17</v>
@@ -47948,16 +47948,16 @@
         <v>110</v>
       </c>
       <c r="AK190">
+        <v>70</v>
+      </c>
+      <c r="AL190">
         <v>60</v>
-      </c>
-      <c r="AL190">
-        <v>55</v>
       </c>
       <c r="AM190">
         <v>75</v>
       </c>
       <c r="AN190">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO190">
         <v>9</v>
@@ -47999,13 +47999,13 @@
         <v>23</v>
       </c>
       <c r="BB190">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC190">
         <v>34</v>
       </c>
       <c r="BD190">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE190">
         <v>55</v>
@@ -48097,7 +48097,7 @@
         <v>579</v>
       </c>
       <c r="F191">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G191">
         <v>3.45</v>
@@ -48106,13 +48106,13 @@
         <v>2.6</v>
       </c>
       <c r="I191">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J191">
         <v>2.8</v>
       </c>
       <c r="K191">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L191">
         <v>1.01</v>
@@ -48145,10 +48145,10 @@
         <v>1.01</v>
       </c>
       <c r="V191">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W191">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X191">
         <v>1000</v>
@@ -48339,7 +48339,7 @@
         <v>580</v>
       </c>
       <c r="F192">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G192">
         <v>4.6</v>
@@ -48348,13 +48348,13 @@
         <v>2.16</v>
       </c>
       <c r="I192">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J192">
         <v>1.1</v>
       </c>
       <c r="K192">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L192">
         <v>1.01</v>
@@ -48372,7 +48372,7 @@
         <v>1.51</v>
       </c>
       <c r="Q192">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R192">
         <v>1.15</v>
@@ -48381,19 +48381,19 @@
         <v>1.01</v>
       </c>
       <c r="T192">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U192">
         <v>1.01</v>
       </c>
       <c r="V192">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="W192">
         <v>1.28</v>
       </c>
       <c r="X192">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y192">
         <v>1000</v>
@@ -48450,55 +48450,55 @@
         <v>7.2</v>
       </c>
       <c r="AQ192">
-        <v>1.11</v>
+        <v>5.7</v>
       </c>
       <c r="AR192">
-        <v>1.11</v>
+        <v>9</v>
       </c>
       <c r="AS192">
-        <v>1.11</v>
+        <v>21</v>
       </c>
       <c r="AT192">
-        <v>1.11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU192">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="AV192">
-        <v>1.11</v>
+        <v>9.4</v>
       </c>
       <c r="AW192">
-        <v>1.11</v>
+        <v>23</v>
       </c>
       <c r="AX192">
-        <v>1.11</v>
+        <v>19.5</v>
       </c>
       <c r="AY192">
-        <v>1.11</v>
+        <v>15.5</v>
       </c>
       <c r="AZ192">
-        <v>1.11</v>
+        <v>19.5</v>
       </c>
       <c r="BA192">
-        <v>1.11</v>
+        <v>44</v>
       </c>
       <c r="BB192">
-        <v>1.11</v>
+        <v>60</v>
       </c>
       <c r="BC192">
-        <v>1.11</v>
+        <v>46</v>
       </c>
       <c r="BD192">
-        <v>1.11</v>
+        <v>70</v>
       </c>
       <c r="BE192">
-        <v>1.11</v>
+        <v>100</v>
       </c>
       <c r="BF192">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BG192">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="BH192">
         <v>1000</v>
@@ -48856,7 +48856,7 @@
         <v>1.64</v>
       </c>
       <c r="Q194">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R194">
         <v>1.18</v>
